--- a/outputs/final_access_results.xlsx
+++ b/outputs/final_access_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Filename</t>
   </si>
@@ -70,13 +70,19 @@
     <t>&gt;=6</t>
   </si>
   <si>
+    <t>Psoriasis: Inadequate response, intolerance or contraindication with TWO of the following: Enbrel, Humira, Otezla, Skyrizi.; Psoriatic Arthritis: Inadequate response, intolerance or contraindication with TWO of the following: Enbrel, Humira, Otezla, Xeljanz/XR.</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>N; A</t>
+    <t>The member has a continued benefit to therapy.; Extension requests where the ustekinumab did not have the full desired effect or considered a clinical failure will require clinical rationale for continuing.</t>
   </si>
 </sst>
 </file>
@@ -494,17 +500,26 @@
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>6</v>
@@ -513,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/final_access_results.xlsx
+++ b/outputs/final_access_results.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hackathon\outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD225CE-0A40-4FCE-AF59-AFEBED2400F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$80</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="263">
   <si>
     <t>Filename</t>
   </si>
@@ -34,18 +43,18 @@
     <t>Number of Steps through Generic</t>
   </si>
   <si>
-    <t>Step through Phototherapy</t>
+    <t>Step through-Phototherapy</t>
   </si>
   <si>
     <t>TB Test required</t>
   </si>
   <si>
+    <t>Quantity Limits</t>
+  </si>
+  <si>
     <t>Specialist Types</t>
   </si>
   <si>
-    <t>Quantity Limits</t>
-  </si>
-  <si>
     <t>Initial Authorization Duration(in-months)</t>
   </si>
   <si>
@@ -61,35 +70,780 @@
     <t>Access Score</t>
   </si>
   <si>
+    <t>148593-4960549.pdf</t>
+  </si>
+  <si>
+    <t>163262-4627017.pdf</t>
+  </si>
+  <si>
+    <t>167126-4508319.pdf</t>
+  </si>
+  <si>
+    <t>176207-4867884.pdf</t>
+  </si>
+  <si>
+    <t>176806-5005129.pdf</t>
+  </si>
+  <si>
+    <t>176810-4889390.pdf</t>
+  </si>
+  <si>
+    <t>183953-4805567.pdf</t>
+  </si>
+  <si>
+    <t>187701-5050284.pdf</t>
+  </si>
+  <si>
+    <t>195158-4643510.pdf</t>
+  </si>
+  <si>
+    <t>195239-4641478.pdf</t>
+  </si>
+  <si>
+    <t>203402-5001149.pdf</t>
+  </si>
+  <si>
+    <t>215824-5041653.pdf</t>
+  </si>
+  <si>
+    <t>247339-4770410.pdf</t>
+  </si>
+  <si>
+    <t>250819-3621812.pdf</t>
+  </si>
+  <si>
+    <t>255515-5050321.pdf</t>
+  </si>
+  <si>
+    <t>255517-4865097.pdf</t>
+  </si>
+  <si>
+    <t>258492-5030356.pdf</t>
+  </si>
+  <si>
+    <t>258503-4913513.pdf</t>
+  </si>
+  <si>
+    <t>269830-4591538.pdf</t>
+  </si>
+  <si>
+    <t>270625-4631548.pdf</t>
+  </si>
+  <si>
+    <t>270849-4873664.pdf</t>
+  </si>
+  <si>
+    <t>273941-4788109.pdf</t>
+  </si>
+  <si>
+    <t>275244-4659838.pdf</t>
+  </si>
+  <si>
+    <t>282478-5009832.pdf</t>
+  </si>
+  <si>
+    <t>283789-5060638.pdf</t>
+  </si>
+  <si>
+    <t>287728-4459856.pdf</t>
+  </si>
+  <si>
+    <t>296792-5001283.pdf</t>
+  </si>
+  <si>
+    <t>296961-4569911.pdf</t>
+  </si>
+  <si>
+    <t>297411-4840622.pdf</t>
+  </si>
+  <si>
+    <t>298309-4972610.pdf</t>
+  </si>
+  <si>
+    <t>299241-4702948.pdf</t>
+  </si>
+  <si>
+    <t>305252-5002815.pdf</t>
+  </si>
+  <si>
+    <t>305769-4866320.pdf</t>
+  </si>
+  <si>
+    <t>308650-4595103.pdf</t>
+  </si>
+  <si>
+    <t>313179-3560271.pdf</t>
+  </si>
+  <si>
+    <t>315085-4653251.pdf</t>
+  </si>
+  <si>
+    <t>324603-4962713.pdf</t>
+  </si>
+  <si>
+    <t>325611-4784675.pdf</t>
+  </si>
+  <si>
+    <t>326557-4901234.pdf</t>
+  </si>
+  <si>
+    <t>330107-4979411.pdf</t>
+  </si>
+  <si>
+    <t>330109-4880941.pdf</t>
+  </si>
+  <si>
+    <t>333345-4841422.pdf</t>
+  </si>
+  <si>
+    <t>337814-4985370.pdf</t>
+  </si>
+  <si>
+    <t>361202-4967201.pdf</t>
+  </si>
+  <si>
+    <t>361486-4654549.pdf</t>
+  </si>
+  <si>
+    <t>362198-4805629.pdf</t>
+  </si>
+  <si>
+    <t>363337-5004251.pdf</t>
+  </si>
+  <si>
+    <t>363896-4716077.pdf</t>
+  </si>
+  <si>
+    <t>364054-4720790.pdf</t>
+  </si>
+  <si>
+    <t>365374-5059388.pdf</t>
+  </si>
+  <si>
+    <t>371611-4978411.pdf</t>
+  </si>
+  <si>
+    <t>372229-5027532.pdf</t>
+  </si>
+  <si>
+    <t>372479-5037971.pdf</t>
+  </si>
+  <si>
+    <t>372505-5024739.pdf</t>
+  </si>
+  <si>
     <t>377585-4984547.pdf</t>
   </si>
   <si>
+    <t>378692-5003182.pdf</t>
+  </si>
+  <si>
+    <t>378792-5004240.pdf</t>
+  </si>
+  <si>
+    <t>379899-5030421.pdf</t>
+  </si>
+  <si>
+    <t>51842-4975862.pdf</t>
+  </si>
+  <si>
+    <t>55182-4590747.pdf</t>
+  </si>
+  <si>
+    <t>56061-4538520.pdf</t>
+  </si>
+  <si>
+    <t>56263-4803097.pdf</t>
+  </si>
+  <si>
+    <t>56403-5061730.pdf</t>
+  </si>
+  <si>
+    <t>58918-4969735.pdf</t>
+  </si>
+  <si>
+    <t>66156-4274314.pdf</t>
+  </si>
+  <si>
+    <t>84074-5053811.pdf</t>
+  </si>
+  <si>
+    <t>8889-4641730.pdf</t>
+  </si>
+  <si>
+    <t>8898-4735285.pdf</t>
+  </si>
+  <si>
+    <t>9023-4381765.pdf</t>
+  </si>
+  <si>
+    <t>9026-4997564.pdf</t>
+  </si>
+  <si>
     <t>STELARA</t>
   </si>
   <si>
+    <t>BIMZELX</t>
+  </si>
+  <si>
+    <t>TREMFYA</t>
+  </si>
+  <si>
+    <t>SKYRIZI</t>
+  </si>
+  <si>
+    <t>OTEZLA</t>
+  </si>
+  <si>
+    <t>YESINTEK</t>
+  </si>
+  <si>
+    <t>OTULFI</t>
+  </si>
+  <si>
+    <t>ENBREL</t>
+  </si>
+  <si>
+    <t>ILUMYA</t>
+  </si>
+  <si>
+    <t>ACITRETIN</t>
+  </si>
+  <si>
+    <t>AMJEVITA</t>
+  </si>
+  <si>
+    <t>SILIQ</t>
+  </si>
+  <si>
+    <t>CIMZIA</t>
+  </si>
+  <si>
+    <t>COSENTYX</t>
+  </si>
+  <si>
+    <t>REMICADE</t>
+  </si>
+  <si>
+    <t>&gt;=12</t>
+  </si>
+  <si>
+    <t>&gt;=18</t>
+  </si>
+  <si>
     <t>&gt;=6</t>
   </si>
   <si>
-    <t>Psoriasis: Inadequate response, intolerance or contraindication with TWO of the following: Enbrel, Humira, Otezla, Skyrizi.; Psoriatic Arthritis: Inadequate response, intolerance or contraindication with TWO of the following: Enbrel, Humira, Otezla, Xeljanz/XR.</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
+    <t>&lt;18</t>
+  </si>
+  <si>
+    <t>&gt;=2</t>
+  </si>
+  <si>
+    <t>Member has a contraindication, intolerance or ineffective response to all of the following available equivalent alternative targeted immune modulators (one-month trial): both Ilumya, Stelara, and either Avsola, Inflectra, or Renflexis.; Member has had an inadequate response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin; or has a clinical reason to avoid these treatments.</t>
+  </si>
+  <si>
+    <t>The member must have experienced therapeutic failure or intolerance to phototherapy (e.g. PUVA, UVB), at least one systemic therapy (e.g., methotrexate), or be contraindicated to both.; The member has experienced therapeutic failure or intolerance to at least two (2) preferred biologic products for the treatment of PsO (see Table 1).</t>
+  </si>
+  <si>
+    <t>Reserved for treatment failure to 12 weeks of dose-optimized, oral DMARD therapy (Methotrexate, Cyclosporine, and Acitretin).; Reserved for treatment failure/documented intolerance to Adalimumab, Etanercept, or Infliximab.; Reserved for treatment failure/documented intolerance to Secukinumab, Guselkumab, Brodalumab, Tildrakizumab, or Ixekizumab.</t>
+  </si>
+  <si>
+    <t>Authorization may be granted for members who have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for the treatment of moderate to severe plaque psoriasis.; Authorization may be granted when the member has had an inadequate response, intolerance, or a clinical reason to avoid phototherapy or pharmacologic treatment with methotrexate, cyclosporine, or acitretin.</t>
+  </si>
+  <si>
+    <t>The member must have previously received a biologic or targeted synthetic drug indicated for the treatment of moderate to severe plaque psoriasis.; Alternatively, if no previous biologic/targeted synthetic drug, the member must have had an inadequate response, intolerance, or a clinical reason to avoid pharmacologic treatment with phototherapy, methotrexate, cyclosporine, or acitretin.</t>
+  </si>
+  <si>
+    <t>Authorization may be granted for adult members who have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for the treatment of moderate to severe plaque psoriasis.; Authorization may be granted for adult members with at least 3% body surface area affected who have had an inadequate response, intolerance, or a clinical reason to avoid pharmacologic treatment with methotrexate, cyclosporine, or acitretin, or phototherapy.</t>
+  </si>
+  <si>
+    <t>Patient must have a minimum duration of a 4-week trial and failure, contraindication, or intolerance to one of the following topical therapies: corticosteroids (e.g., betamethasone, clobetasol), vitamin D analogs (e.g., calcitriol, calcipotriene), tazarotene, or calcineurin inhibitors (e.g., tacrolimus, pimecrolimus).</t>
+  </si>
+  <si>
+    <t>The patient must have had a 3-month trial of systemic therapy (i.e., acitretin, methotrexate, or cyclosporine) that resulted in an inadequate response (failure), or a 3-month trial of Ultraviolet B (UVB) Phototherapy or Psoralen Ultraviolet A (PUVA) Phototherapy that resulted in an inadequate response (failure).</t>
+  </si>
+  <si>
+    <t>For moderate to severe plaque psoriasis (new starts only), the patient must have experienced an inadequate treatment response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin, OR these treatments are contraindicated, OR the patient has severe psoriasis that warrants a biologic as first-line therapy (i.e., at least 10% of the body surface area or crucial body areas are affected).</t>
+  </si>
+  <si>
+    <t>For plaque psoriasis, the member must have a history of trial and failure of ONE of the following: 1) topical therapy (e.g. corticosteroid, calcineurin inhibitor, vitamin D analog), 2) phototherapy, 3) systemic treatment (e.g. methotrexate, cyclosporine, oral retinoids).</t>
+  </si>
+  <si>
+    <t>Member must use all of the following preferred biosimilars (unless contraindicated or adverse effects experienced): Otulfi, Pyzchiva (branded), Selarsdi (or unbranded ustekinumab-aekn), Steqeyma.; Member must fail a 3 consecutive month trial of methotrexate (MTX), or if intolerant/contraindicated, fail a trial of cyclosporine or acitretin, or if intolerant/contraindicated to those, fail phototherapy.</t>
+  </si>
+  <si>
+    <t>Patient has tried at least one traditional systemic agent for psoriasis for at least 3 months, or a 3-month trial of psoralen plus ultraviolet A light (PUVA).; An exception to the requirement for a trial of one traditional systemic agent for psoriasis can be made if the patient has already had a 3-month trial or previous intolerance to at least one biologic other than the requested drug.</t>
+  </si>
+  <si>
+    <t>Member must use Stelara.; Member must experience failure of ONE of the following adalimumab products or Enbrel (unless the member has had a history of failure of two TNF blockers).; Member must experience failure of THREE of the following: Otezla, Skyrizi, Tremfya, Cosentyx.</t>
+  </si>
+  <si>
+    <t>Member must have a documented inadequate response, intolerance, or contraindication to at least one oral systemic therapy such as methotrexate or cyclosporine for 3 months or more.; As a non-preferred Cytokine and Cell Adhesion Molecule (CAM) Antagonist, the member must trial and fail one preferred anti-TNF (Enbrel or Humira/Amjevita Auto-Injector).</t>
+  </si>
+  <si>
+    <t>Documented inadequate response, intolerance, or contraindication, to at least one oral systemic therapy such as methotrexate, or cyclosporine for 3 months or more.; Non-Preferred Cytokines and Cell Adhesion Molecule (CAM) Antagonists require trial and failure of ONE preferred anti-TNF (Enbrel or Humira/Amjevita Auto-Injector) OR Kevzara, where indicated.</t>
+  </si>
+  <si>
+    <t>Patient must have a history of failure to one of the following topical therapies: corticosteroids, vitamin D analogs, tazarotene, calcineurin inhibitors, anthralin, or coal tar.; Patient must have a history of failure to a 3 month trial of methotrexate at maximally indicated dose.; Alternatively, patient has been previously treated with a targeted immunomodulator FDA-approved for the treatment of plaque psoriasis.</t>
+  </si>
+  <si>
+    <t>Patient must have a history of failure to one of the following topical therapies: Corticosteroids, Vitamin D analogs, Tazarotene, Calcineurin inhibitors, Anthralin, or Coal tar.; Patient must have a history of failure to a 3 month trial of methotrexate at maximally indicated dose, OR have been previously treated with a targeted immunomodulator FDA-approved for the treatment of plaque psoriasis.</t>
+  </si>
+  <si>
+    <t>The member must have a documented inadequate response, intolerable adverse event or contraindication to ALL of the following: Cosentyx SQ, Enbrel, Otezla, Skyrizi SQ, Stelara SQ, Taltz, Tremfya SQ, and adalimumab-adaz, Hyrimoz (Cordavis) or Hadlima, Pyzchiva SQ (Cordavis or Sandoz), Yesintek SQ OR Stelara SQ.</t>
+  </si>
+  <si>
+    <t>Authorization of 12 months may be granted for adult members who have previously received a biologic or targeted synthetic drug indicated for the treatment of moderate to severe plaque psoriasis.; Member has had an inadequate response or intolerance to either phototherapy or pharmacologic treatment with methotrexate, cyclosporine or acitretin, or has a clinical reason to avoid these pharmacologic treatments.</t>
+  </si>
+  <si>
+    <t>The member must have experienced therapeutic failure or intolerance to at least one (1) systemic therapy (e.g., methotrexate) or phototherapy (e.g., PUVA, UVB), or be contraindicated to both.; The member has experienced therapeutic failure or intolerance to at least two (2) step 1 or 2 plan-preferred agents for the treatment of PsO.</t>
+  </si>
+  <si>
+    <t>Documentation of inadequate response to one of the following topical therapies: a corticosteroid, a vitamin D analog, tazarotene, calcineurin inhibitor, anthralin, or coal tar.; Alternatively, documentation of previous treatment with a biologic agent indicated for the requested use.</t>
+  </si>
+  <si>
+    <t>Documentation of an inadequate response or adverse reaction to at least a three consecutive month trial of a combination of conventional therapies (topical, systemic, phototherapy) or a contraindication to all conventional therapies, OR an inadequate response or adverse reaction to at least a three consecutive month trial of one biologic DMARD.; Documentation of an inadequate response or adverse reaction to at least a three consecutive month trial of Enbrel, Humira, preferred adalimumab biosimilars, infliximab, Otezla, or Taltz, OR a contraindication to all of these agents.</t>
+  </si>
+  <si>
+    <t>The member must have an inadequate response or adverse reaction to at least a 3-month trial of one biologic DMARD that is FDA-approved for plaque psoriasis, OR an inadequate response or adverse reaction to at least a 3-month trial of one conventional therapy combination (topical/systemic, topical/phototherapy, systemic/phototherapy, or two systemic agents), OR a contraindication to methotrexate.</t>
+  </si>
+  <si>
+    <t>Member must have an inadequate response or adverse reaction to one biologic DMARD that is FDA-approved for plaque psoriasis, OR an inadequate response or adverse reaction to a 3 consecutive month trial of specified combinations (topical/systemic/phototherapy), OR a contraindication to methotrexate.</t>
+  </si>
+  <si>
+    <t>For moderate to severe Chronic Plaque Psoriasis, individual has had inadequate response to, or is intolerant of, phototherapy OR ONE other systemic therapies (such as, methotrexate, acitretin, or cyclosporine) OR has a contraindication to phototherapy, acitretin, cyclosporine, and methotrexate.</t>
+  </si>
+  <si>
+    <t>Trial of all preferred formulary agents is required unless all are contraindicated, resulting in an inadequate response after four consecutive months of use per medication or a severe adverse reaction.; Trials of two local therapies and one systemic therapy are required unless all are contraindicated, resulting in an inadequate response after four consecutive months of use per medication or a severe adverse reaction.</t>
+  </si>
+  <si>
+    <t>Trials of two local therapies and one systemic therapy are required unless all are contraindicated, resulting in an inadequate response after four consecutive months of use per medication or a severe adverse reaction.</t>
+  </si>
+  <si>
+    <t>History of trial and failure of at least TWO of the following conventional therapies at maximally tolerated doses (TWO months of each) unless contraindicated or clinically significant adverse effects are experienced: Topical corticosteroids, Acitretin, Topical Vitamin D analogs, Calcineurin inhibitors, Topical retinoic acid derivatives, or Phototherapy.</t>
+  </si>
+  <si>
+    <t>Patient must have a history of trial and failure of at least TWO of the following conventional therapies at maximally tolerated doses (TWO months of each) unless contraindicated or clinically significant adverse effects are experienced: Topical corticosteroids, Acitretin, Topical Vitamin D analogs, Calcineurin inhibitors, Topical retinoic acid derivatives, or Phototherapy.</t>
+  </si>
+  <si>
+    <t>Trial and failure of ≥ 3 months of at least one (1) conventional systemic therapy (methotrexate, cyclosporin, acitretin) or phototherapy (psoralen plus ultraviolet A light), unless contraindicated or clinically significant adverse effects are experienced.</t>
+  </si>
+  <si>
+    <t>Trial and failure of ≥ 3 months of at least one (1) conventional systemic therapy, unless contraindicated or clinically significant adverse effects are experienced: Methotrexate [MTX], Cyclosporine, Acitretin, or Phototherapy (psoralen plus ultraviolet A light [PUVA]).</t>
+  </si>
+  <si>
+    <t>Member has had an inadequate response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin; or member has a clinical reason to avoid pharmacologic treatment with methotrexate, cyclosporine, and acitretin.</t>
+  </si>
+  <si>
+    <t>Patient did not respond adequately (or is not a candidate) to a 4-week minimum trial of at least TWO (2) therapeutically different topical agents.; Patient did not respond adequately (or is not a candidate) to a 3-month minimum trial of at least ONE (1) non-biologic systemic agent.; Patient did not respond adequately (or is not a candidate*) to a 3-month minimum trial of phototherapy (i.e., psoralens with UVA light [PUVA] or UVB with coal tar or dithranol).</t>
+  </si>
+  <si>
+    <t>Patient must be unresponsive to at least 2 conventional therapies including topical corticosteroids, vitamin D analogs, Tazorac, topical tacrolimus, Elidel, or phototherapy.</t>
+  </si>
+  <si>
+    <t>Plaque psoriasis preferred agents require evidence of failure after at least 90 days of topical therapy with two different agents classified as an emollient, corticosteroid, topical retinoid or vitamin D analog.; A 90-day trial of one DMARD (or a systemic retinoid such as acitretin) is also required.</t>
+  </si>
+  <si>
+    <t>Patient must have tried and had an inadequate response to, an intolerance or hypersensitivity to, or an FDA labeled contraindication to at least ONE conventional prerequisite agent for the requested indication.; Alternatively, patient's medication history indicates use of a biologic immunomodulator agent for the same FDA labeled indication.</t>
+  </si>
+  <si>
+    <t>Member must have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for treatment of moderate to severe plaque psoriasis.; Member must have had an inadequate response, intolerance, or a clinical reason to avoid pharmacologic treatment with methotrexate, cyclosporine, or acitretin, or phototherapy (e.g., UVB, PUVA).</t>
+  </si>
+  <si>
+    <t>The member must have an inadequate response or adverse reaction to at least a 3 month trial of ONE biologic DMARD that is FDA-approved for plaque psoriasis, OR an inadequate response or adverse reaction to at least a 3 month trial of specified combinations of conventional therapies.; The member must have an inadequate response or adverse reaction to at least 3 months of treatment with ONE of the PDL preferred agents: Enbrel, preferred adalimumab biosimilar, Humira, infliximab, Otezla, or Taltz, OR a contraindication to all of those agents.</t>
+  </si>
+  <si>
+    <t>If the client has preferred agents, the patient must have tried and had an inadequate response to one or more preferred agents after at least a 3-month duration of therapy per agent, or have an intolerance/hypersensitivity or contraindication to the preferred agents.</t>
+  </si>
+  <si>
+    <t>Authorization of 12 months may be granted for members 6 years of age and older who have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for treatment of moderate to severe plaque psoriasis.; Authorization of 12 months may be granted for members 6 years of age and older for treatment of moderate to severe plaque psoriasis when the member has an inadequate response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin (or a clinical reason to avoid these agents).</t>
+  </si>
+  <si>
+    <t>The patient is unable to take three preferred products (a preferred ustekinumab product, a preferred adalimumab product OR Enbrel, Rinvoq, or Otezla) for the given diagnosis due to a trial and inadequate treatment response or intolerance, or a contraindication.; The member has had an inadequate response or intolerance to either phototherapy or pharmacologic treatment with methotrexate, cyclosporine, or acitretin OR has a clinical reason to avoid pharmacologic treatment with methotrexate, cyclosporine, and acitretin.</t>
+  </si>
+  <si>
+    <t>Documented failure, intolerance, or contraindication to topical therapy (topical corticosteroids, vitamin D analogs, etc).</t>
+  </si>
+  <si>
+    <t>Inadequate response to a trial of one or more of the preferred products.</t>
+  </si>
+  <si>
+    <t>The member must have an inadequate response to a trial of one or more of the preferred products: Entyvio IV (vedolizumab), Inflectra (infliximab-dyyb), or Renflexis (infliximab-abda).</t>
+  </si>
+  <si>
+    <t>Has tried and failed a TNF blocker.; Has tried and failed at least one other therapy to include at least one topical agent.</t>
+  </si>
+  <si>
+    <t>Member must demonstrate failure of a three-month trial of at least one oral agent (methotrexate, cyclosporine, or acitretin) OR a 30-treatment course of photochemotherapy or phototherapy.; Member must fail a therapeutic trial of ALL HAP preferred anti-TNF agents (unless clinically significant medical contraindications are documented).; Member must fail a therapeutic trial (3 months) of oral apremilast.</t>
+  </si>
+  <si>
+    <t>For plaque psoriasis (initial requests): One of the following was ineffective or not tolerated: a) methotrexate at a dose of at least 10mg/week (or maximally tolerated dose) OR b) acitretin (trial of other agents not required for patients under 18 years of age).</t>
+  </si>
+  <si>
+    <t>Documentation of an inadequate response or adverse reaction to at least a 3 month trial of one biologic DMARD or two conventional therapies in defined combinations, or a contraindication to methotrexate.; Documentation of an inadequate response or adverse reaction or contraindication to Enbrel or Humira.</t>
+  </si>
+  <si>
+    <t>For plaque psoriasis (initial requests): One of the following was ineffective or not tolerated: a) methotrexate at a dose of at least 10mg/week (or maximally tolerated dose) OR b) acitretin.</t>
+  </si>
+  <si>
+    <t>The patient must have a history of failure to phototherapy (UVB or PUVA) or treatment with at least one non-Cytokine and CAM DMARD (e.g., methotrexate, cyclosporine, acitretin, azathioprine, etc.) [minimum trial of 12 weeks].; For brand name ustekinumab (Stelara), treatment with two preferred Cytokine and CAM Apple Health Preferred Drug List (PDL) medications has each been ineffective, unless all are contraindicated, or not tolerated [minimum trial of 12 weeks].</t>
+  </si>
+  <si>
+    <t>The patient must have a history of failure to phototherapy (UVB or PUVA) or treatment with at least one non-Cytokine and CAM DMARD (e.g., methotrexate, cyclosporine, acitretin, azathioprine, etc.) for a minimum trial of 12 weeks.; Treatment with two preferred Cytokine and CAM Apple Health Preferred Drug List (PDL) medications must have each been ineffective, unless all are contraindicated or not tolerated, for a minimum trial of 12 weeks.</t>
+  </si>
+  <si>
+    <t>Member has had a minimum duration of a 4-week trial and failure, or intolerance to ONE of the following topical therapies or contraindication to ALL of them: Corticosteroids, Vitamin D analogs, Tazarotene, Calcineurin inhibitors, Anthralin, Coal tar.</t>
+  </si>
+  <si>
+    <t>Member must provide documentation of moderate to severe chronic plaque psoriasis with an inadequate response, intolerance or contraindication with two of the following therapies: Enbrel, Humira, Otezla, Skyrizi.</t>
+  </si>
+  <si>
+    <t>Authorization for plaque psoriasis may be granted for members who have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for treatment of moderate to severe plaque psoriasis.; Authorization for plaque psoriasis may be granted for members who have had an inadequate response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin.; The patient is unable to take THREE preferred products, where indicated, for the given diagnosis due to a trial and inadequate treatment response or intolerance, or a contraindication.</t>
+  </si>
+  <si>
+    <t>Authorization may be granted for adult members who have previously received a biologic or targeted synthetic drug indicated for the treatment of moderate to severe plaque psoriasis.; Member has had an inadequate response or intolerance to either phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin.; The patient is unable to take THREE preferred products, where indicated, for the given diagnosis due to a trial and inadequate treatment response or intolerance, or a contraindication.</t>
+  </si>
+  <si>
+    <t>Authorization of 12 months may be granted for members 6 years of age and older who have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for treatment of moderate to severe plaque psoriasis.; Authorization of 12 months may be granted for members 6 years of age and older for treatment of moderate to severe plaque psoriasis when the member has had an inadequate response or intolerance to, or a clinical reason to avoid, phototherapy (e.g., UVB, PUVA) or pharmacologic treatment with methotrexate, cyclosporine, or acitretin.</t>
+  </si>
+  <si>
+    <t>Patient must have a history of failure to one of the following topical therapies: corticosteroids, vitamin D analogs, tazarotene, calcineurin inhibitors, anthralin, or coal tar, unless contraindicated or clinically significant adverse effects are experienced.; Patient must have a history of failure to a 3 month trial of methotrexate at the maximally indicated dose, unless contraindicated or clinically significant adverse effects are experienced.; Alternatively, the patient must have been previously treated with a targeted immunomodulator FDA-approved for the treatment of plaque psoriasis.</t>
+  </si>
+  <si>
+    <t>Patient must try one Step 1 agent, which includes SQ agents: Cosentyx, Enbrel, Hadlima, Humira, Simlandi, Skyrizi, Stelara, Tremfya; or Oral agent: Otezla.</t>
+  </si>
+  <si>
+    <t>Has trialed and failed a TNF blocker.; Has trialed and failed at least one other therapy to include at least one topical agent.</t>
+  </si>
+  <si>
+    <t>Patient must complete a minimum duration of a 4-week trial and failure, contraindication, or intolerance to one of the following topical therapies: corticosteroids (e.g., betamethasone, clobetasol), vitamin D analogs (e.g., calcitriol, calcipotriene), tazarotene, or calcineurin inhibitors (e.g., tacrolimus, pimecrolimus).</t>
+  </si>
+  <si>
+    <t>Client must have diagnosis and a 56-day trial and failure of two of the three preferred agents (ENBREL, HUMIRA, OTEZLA).</t>
+  </si>
+  <si>
+    <t>The member must have previously received a biologic or targeted synthetic drug (e.g., Sotyktu, Otezla) indicated for treatment of moderate to severe plaque psoriasis.; For members with at least 3% body surface area (BSA) affected, the member must have had an inadequate response, intolerance, or clinical reason to avoid pharmacologic treatment with methotrexate, cyclosporine, or acitretin, or phototherapy (e.g., UVB, PUVA).</t>
+  </si>
+  <si>
+    <t>Patient did not respond adequately (or is not a candidate) to a trial of topical agents (i.e., corticosteroids).; Patient did not respond adequately (or is not a candidate) to a trial of phototherapy (i.e., psoralens with UVA light [PUVA] or UVB with coal tar or dithranol).</t>
+  </si>
+  <si>
+    <t>The patient must try one preferred biologic (adalimumab product(s), Cosentyx, or Enbrel) or preferred oral agent (Rinvoq, Xeljanz, or Xeljanz XR) as a Step 1 therapy for their diagnosis.</t>
+  </si>
+  <si>
+    <t>The individual has failed (≥3 months use) previous treatment with at least ONE of the listed conventional agents (Methotrexate, Cyclosporine, Psoralen with UVA radiation, UVB &amp; coal tar on ditranol, Acitretin, or Narrow Band UVB).</t>
+  </si>
+  <si>
+    <t>The patient must have tried at least one of the following for at least 3 months: oral therapy for psoriasis (e.g., MTX, cyclosporine, Soriatane), oral methoxsalen plus ultraviolet A light (PUVA), or a biologic agent (e.g., Humira, Remicade, or Stelara).; An exception to the requirement for a trial of one traditional systemic agent for psoriasis can be made if the patient has had a 3-month trial or previous intolerance to at least one biologic (e.g., Cosentyx, an adalimumab product, an infliximab product, Siliq, Stelara, Taltz, or Tremfya).</t>
+  </si>
+  <si>
+    <t>Patient must try and have an inadequate response, contraindication, or intolerance to a 3-month trial of AVSOLA AND INFLECTRA.; Patient did not respond adequately (or is not a candidate) to a 4-week minimum trial of topical agents (i.e., anthralin, coal tar preparations, corticosteroids, emollients, immunosuppressives, keratolytics, tapinarof, roflumilast, retinoic acid derivatives, and/or vitamin D analogues).; Patient did not respond adequately (or is not a candidate) to a 3-month minimum trial of at least one non-biologic systemic agent (i.e., immunosuppressives, retinoic acid derivatives, and/or methotrexate).; Patient did not respond adequately (or is not a candidate) to a 3-month minimum trial of phototherapy (i.e., psoralens with UVA light [PUVA] or UVB with coal tar or dithranol).</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>The member has a continued benefit to therapy.; Extension requests where the ustekinumab did not have the full desired effect or considered a clinical failure will require clinical rationale for continuing.</t>
+    <t>Ten (10) autoinjectors/prefilled syringes within the first sixteen (16) weeks of therapy; Two (2) autoinjectors/prefilled syringes every eight (8) weeks; Two (2) autoinjectors/prefilled syringes every four (4) weeks; Two (2) autoinjectors/prefilled syringes every eight (8) weeks</t>
+  </si>
+  <si>
+    <t>Ustekinumab 130 mg/26 mL single-dose vial CD, UC intravenous induction 
+• 
+≤ 55 kg: 260 mg (2 vials) 
+• 
+&gt; 55 kg to 85 kg: 390 mg (3 vials) 
+• 
+&gt; 85 kg: 520 mg (4 vials); Ustekinumab subcutaneous injection 45 mg/0.5 mL vial/syringe Psoriasis (6 years and older)/ Psoriasis with or without co-existent PsA (adult) 
+• 
+≤ 100 kg: 2 vials/syringes per first 28 days (load); 1 vial/syringe every 12 weeks (maintenance) 
+• 
+&gt; 100 kg: 2 vials/syringes per first 28 days (load); 1 vial/syringe every 12 weeks (maintenance) 
+PsA (6 years and older), without co-existent plaque psoriasis 
+• 
+2 vials/syringes per first 28 days (load) 
+• 
+1 vial/syringe every 12 weeks (maintenance) 
+CD, UC maintenance dose 
+• 
+1 syringe every 8 weeks; Ustekinumab subcutaneous injection 90 mg/mL syringe Psoriasis (6 years and older)*/ Psoriasis with or without co-existent PsA (adult) 
+• 
+≤ 100 kg: 45 mg initially and 4 weeks later, followed by 45 mg every 12 weeks 
+• 
+&gt; 100 kg: 90 mg initially and 4 weeks later, followed by 90 mg every 12 weeks 
+CD*, UC maintenance dose 
+• 
+1 syringe every 8 weeks</t>
+  </si>
+  <si>
+    <t>Initiation of therapy: 2 syringes/injectors per first 28 days; Maintenance: 1 syringe/injector per 56 days; Initiation of therapy: three vials per first 56 days OR six 200 mg pens (CD only); Maintenance: 100 mg syringe/injector per 56 days OR 200 mg pen/syringe per 28 days</t>
+  </si>
+  <si>
+    <t>100mg/mL (autoinjector, prefilled syringe) 1mL per 56 days; 200mg/2mL (autoinjector, prefilled syringe) 2mL per 28 days; Induction Pack for Crohn’s Disease (2 x 200 mg/2 mL single-dose prefilled pens): 4 mL/365 days; A maximum of 12 mL/56 days will be granted to allow for completion of induction dosing during the first 8 weeks of treatment</t>
+  </si>
+  <si>
+    <t>Two (2) prefilled syringes within the first four (4) weeks of therapy; One (1) prefilled syringe every twelve (12) weeks</t>
+  </si>
+  <si>
+    <t>Adults ≤ 100 kg: One 45 mg syringe or vial for the first 28 days, then one 45 mg syringe or vial every 12 weeks; Adults &gt; 100 kg: One 90 mg syringe for the first 28 days, then one 90 mg syringe every 12 weeks; Pediatrics &lt; 60 kg: 0.75 mg/kg; Pediatrics 60 kg to 100 kg: One 45 mg syringe or vial for the first 28 days, then one 45 mg syringe or vial every 12 weeks; Pediatrics &gt; 100 kg: One 90 mg syringe for the first 28 days, then one 90 mg syringe every 12 weeks; Concurrent PsA and PsO for adults and pediatrics &gt; 100 kg: One 90 mg syringe for the first 28 days, then one 90 mg syringe every 12 weeks; CD and UC: Single intravenous infusion induction dose: ≤ 55 kg: 260 mg (two 130 mg vials), 55.1 kg to 85 kg: 390 mg (three 130 mg vials), &gt; 85 kg: 520 mg (four 130 mg vials); CD and UC: Maintenance: One 90 mg syringe at week 8, then every 8 weeks</t>
+  </si>
+  <si>
+    <t>CD: 200 mg administered by intravenous infusion OR two 200 mg syringe or pen every 28 days for 3 months, then one 100 mg syringe or pen every 8 weeks beginning at week 16 OR one 200 mg syringe or pen every 4 weeks beginning at week 12.; PsO, PsA: 1 syringe or autoinjector for the first 28 days, then 1 syringe or autoinjector every 8 weeks; UC: 200 mg administered by intravenous at Week 0, Week 4, and Week 8, then one 100 mg syringe or pen every 8 weeks beginning at Week 16 OR one 200 mg syringe or pen every 4 weeks beginning at Week 12</t>
+  </si>
+  <si>
+    <t>Ustekinumab 45 mg vial/prefilled syringe: Loading: 1 syringe at weeks 0 &amp; 4; Maintenance: 1 syringe every 12 weeks; Ustekinumab 90 mg prefilled syringe: Loading: 1 syringe at weeks 0 &amp; 4; Maintenance: 1 syringe every 8 weeks</t>
+  </si>
+  <si>
+    <t>Yesintek (ustekinumab-kfce) 130 mg/26 mL single-dose vial: 4 vials (1 dose); Yesintek (ustekinumab-kfce) subcutaneous injection 45 mg/0.5 mL single-dose vial/prefilled syringe: 1 vial/syringe per 84 days; Exception limit: 2 vials/syringes per 28 days; Yesintek (ustekinumab-kfce) subcutaneous injection 90 mg/mL prefilled syringe: 1 syringe per 56 days; Exception limit: 2 syringes per 28 days</t>
+  </si>
+  <si>
+    <t>Tremfya (guselkumab) 100 mg/mL prefilled syringe/One-press injector: 1 syringe/injector per 56 days; Exception limit: 2 syringes/injectors per 28 days; Tremfya (guselkumab) 200 mg/2 mL prefilled syringe/pen: 1 syringe/pen per 28 days; Exception limit: 6 syringes/pens per 56 days; Tremfya (guselkumab) 200 mg/2 mL prefilled pen Induction Pack for Crohn’s Disease: Exception limit: 3 cartons (6 pens) per 56 days</t>
+  </si>
+  <si>
+    <t>Plaque psoriasis and psoriatic arthritis: 100mg strength only: 2/28 for the first month then 1/56; Ulcerative Colitis: IV: 200 mg vial: 2 for the first month, 1 for month 2; Ulcerative Colitis: Subq: 200mg: 1 inj per month, 100mg: 1 inj every 2 months; Crohn’s disease: IV: 200 mg vial: 2 for the first month, 1 for month 2; Crohn’s disease: Subq: 200mg: 4 inj for the 1st month, 2 inj for the 2nd month, then 1 inj per month, 100mg: 1 inj every 2 months; Plaque psoriasis and psoriatic arthritis: 100mg strength only 1/56; Ulcerative Colitis: Subq: 200mg: 1 inj per month, 100mg: 1 inj every 2 months; Crohn’s disease: Subq: 200mg: 1 inj per month, 100mg: 1 inj every 2 months</t>
+  </si>
+  <si>
+    <t>Psoriasis: quantity limit 1 injection/4 weeks for the first 2 fills, followed by 1 injection/12 weeks.; Psoriatic arthritis: quantity limit 1 injection/4 weeks for the first 2 fills, followed by 1 injection/12 weeks.; Crohn’s disease: quantity limit 1 injection/8 weeks; Ulcerative colitis: quantity limit 1 injection/8 weeks; Psoriasis: quantity limit 1 injection/12 weeks; Psoriatic arthritis: quantity limit 1 injection/12 weeks.; Crohn’s disease: quantity limit 1 injection/8 weeks; Ulcerative colitis: quantity limit 1 injection/8 weeks</t>
+  </si>
+  <si>
+    <t>Stelara (ustekinumab) 130 mg/26 mL singledose vial: 4 vials (1 dose); Stelara (ustekinumab) subcutaneous injection 45 mg/0.5 mL single-dose vial/prefilled syringe: 1 vial/syringe per 84 days; Exception limit: 2 vials/syringes per 28 days; Stelara (ustekinumab) subcutaneous injection 90 mg/mL prefilled syringe: 1 syringe per 56 days; Exception limit: 2 syringes per 28 days</t>
+  </si>
+  <si>
+    <t>45 mg per dose; weight up to 100 kg; 90 mg per dose; weight greater than 100 kg for Plaque Psoriasis indications; 90 mg per dose; Crohn’s Disease and Ulcerative Colitis after initial IV infusion.</t>
+  </si>
+  <si>
+    <t>Amjevita adalimumab-atto soln auto-injector 40 MG/0.4ML 2 Pens 28 DAYS; Amjevita adalimumab-atto soln auto-injector 40 MG/0.8ML 2 Pens 28 DAYS; Amjevita adalimumab-atto soln auto-injector 80 MG/0.8ML 2 Pens 28 DAYS; Amjevita adalimumab-atto soln prefilled syringe 10 MG/0.2ML 2 Syringes 28 DAYS; Amjevita adalimumab-atto soln prefilled syringe 20 MG/0.2ML 2 Syringes 28 DAYS</t>
+  </si>
+  <si>
+    <t>dermatologist</t>
+  </si>
+  <si>
+    <t>dermatologist, rheumatologist</t>
+  </si>
+  <si>
+    <t>dermatologist, gastroenterologist, rheumatologist</t>
+  </si>
+  <si>
+    <t>dermatologist, rheumatologist, gastroenterologist</t>
+  </si>
+  <si>
+    <t>gastroenterologist</t>
+  </si>
+  <si>
+    <t>dermatologist, rheumatologist, pulmonologist, ophthalmologist</t>
+  </si>
+  <si>
+    <t>rheumatologist, immunologist, dermatologist, gastroenterologist, colorectal surgeon</t>
+  </si>
+  <si>
+    <t>Dermatologist, Rheumatologist, Gastroenterologist, Hematologist, Oncologist</t>
+  </si>
+  <si>
+    <t>dermatologist, rheumatologist, gastroenterologist, hematologist, oncologist</t>
+  </si>
+  <si>
+    <t>Unspecified</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>The policy states that for plaque psoriasis (PsO), authorization may be granted for members who achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition when there is a reduction in body surface area (BSA) affected from baseline or improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).; The document requires chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms for continuation requests.</t>
+  </si>
+  <si>
+    <t>Chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.; The document states authorization of 12 months may be granted for all members (including new members) who are using the requested medication for moderate to severe plaque psoriasis and who achieve or maintain positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition when any of the following is met: 1. Reduction in body surface area (BSA) affected from baseline 2. Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain)</t>
+  </si>
+  <si>
+    <t>The policy states that continuation of therapy may be granted for members who 'achieve or maintain positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition' when any of the following is met: Reduction in body surface area (BSA) affected from baseline, or Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).; The policy requires: 'Chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.'</t>
+  </si>
+  <si>
+    <t>Reduction in the body surface area (BSA) involvement from baseline; Improvement in symptoms (e.g., pruritus, inflammation) from baseline</t>
+  </si>
+  <si>
+    <t>The policy states: 'For reauthorization: must have documentation from prescriber indicating stabilization or improvement in condition.'</t>
+  </si>
+  <si>
+    <t>The policy states that for continued therapy, the member must be responding positively to therapy.; The policy states the member must meet one of the following: currently receiving medication via Centene benefit or member has previously met initial approval criteria; or member is currently receiving medication and is enrolled in a state and product with continuity of care regulations.; The policy states the request must be for the SC formulation.; The policy states for requests other than the following preferred biosimilars, member must use all of the following preferred biosimilars, unless clinically significant adverse effects are experienced or all are contraindicated: Otulfi, Pyzchiva (branded), Selarsdi (or unbranded ustekinumab-aekn), Steqeyma, Yesintek.; The policy states the member does not have combination use with biological disease-modifying antirheumatic drugs or Janus kinase inhibitors.; The policy states that if the request is for a dose increase, the new dose does not exceed the specific weight-based/condition-based guidelines provided.</t>
+  </si>
+  <si>
+    <t>The policy states that for a patient currently taking Tremfya, the timeframe for established on therapy was changed from 90 days to 3 months.; The policy requires that a response to therapy be ascertained after 12 weeks of continuous therapy.</t>
+  </si>
+  <si>
+    <t>The policy states that for other indications (Section II, Part E), the member must be currently receiving medication via Centene benefit or have previously met initial approval criteria.; The policy states that for other indications (Section II, Part E), the member must provide documentation of positive response to therapy (e.g., for AD: reduction in itching and scratching; for HS: 25% reduction in inflammatory nodules; for RA: decrease in CDAI or RAPID3 score).</t>
+  </si>
+  <si>
+    <t>Documentation indicating member has shown improvement in signs and symptoms of disease</t>
+  </si>
+  <si>
+    <t>Documentation of positive clinical response to the requested ustekinumab therapy</t>
+  </si>
+  <si>
+    <t>Documentation of positive clinical response to Tremfya therapy; Patient is not receiving Tremfya in combination with another targeted immunomodulator</t>
+  </si>
+  <si>
+    <t>The member must achieve or maintain a positive clinical response from Tremfya therapy as evidenced by low disease activity or improvement in signs and symptoms of the condition.; Reduction in body surface area (BSA) affected from baseline.; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).</t>
+  </si>
+  <si>
+    <t>The policy states: 'Approve Enbrel (initial therapy for a duration as directed or 1 year for a patient continuing therapy) if the patient meets the standard Inflammatory Conditions – Enbrel Prior Authorization Policy criteria.'</t>
+  </si>
+  <si>
+    <t>The prescriber attests that the member has demonstrated disease stability or a beneficial response to therapy.</t>
+  </si>
+  <si>
+    <t>The member has had a positive response to therapy; Documentation of clinical justification to continue therapy with the requested medication</t>
+  </si>
+  <si>
+    <t>Initial criteria have been met; The member has had a positive response to therapy; Documentation of clinical justification to continue therapy with the requested medication</t>
+  </si>
+  <si>
+    <t>The policy states there is clinically significant improvement or stabilization in clinical signs and symptoms of the disease.; The policy states the individual has been receiving and is maintained on a stable dose of etanercept.</t>
+  </si>
+  <si>
+    <t>Decreased or sustained reduction in disease activity.; Adherence [must meet one listed below]:</t>
+  </si>
+  <si>
+    <t>Decreased or sustained reduction in disease activity.; Adherence</t>
+  </si>
+  <si>
+    <t>Documentation of positive clinical response to therapy; Patient is not receiving medication with another BRM; Patient is monitored for active TB during treatment (where applicable); Patient is monitored for lymphoma and other malignancies during treatment (where applicable)</t>
+  </si>
+  <si>
+    <t>The policy states: 'Member is currently receiving medication in the past 120 days that has been authorized by RxAdvance or the member has met initial approval criteria.'</t>
+  </si>
+  <si>
+    <t>The policy states that re-authorization requires an updated letter of medical necessity or progress notes showing improvement or maintenance with the medication.</t>
+  </si>
+  <si>
+    <t>The policy states: 'Member is currently receiving medication that has been authorized by RxAdvance or the member has met initial approval criteria.'</t>
+  </si>
+  <si>
+    <t>The policy states that for plaque psoriasis, the member must achieve or maintain positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; The policy states that evidence of response to therapy includes a reduction in body surface area (BSA) affected from baseline or improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).</t>
+  </si>
+  <si>
+    <t>The policy states that the patient must continue to meet the universal and other indication-specific relevant criteria identified in section III.; The policy states that there must be an absence of unacceptable toxicity from the drug.; The policy states that the patient must demonstrate disease response as indicated by improvement in signs and symptoms compared to baseline such as redness, thickness, scaliness, and/or the amount of surface area involvement (a total BSA involvement ≤ 1%), and/or an improvement on a disease activity scoring tool [e.g., a 75% reduction in the PASI score from when treatment started (PASI 75) or a 50% reduction in the PASI score (PASI 50) and a four-point reduction in the DLQI from when treatment started].</t>
+  </si>
+  <si>
+    <t>Documentation of continued effectiveness.; For females able to bear children: Documentation of required pregnancy monitoring AND continued effectiveness.</t>
+  </si>
+  <si>
+    <t>Patient has been previously approved for the requested agent through the plan’s Prior Authorization criteria; Patient has a diagnosis of plaque psoriasis, active psoriatic arthritis, or oral ulcers associated with Behcet’s disease (BD); Patient has had clinical benefit with the requested agent (slowing of disease progression or decrease in symptom severity and/or frequency)</t>
+  </si>
+  <si>
+    <t>The policy states that for plaque psoriasis (PsO), authorization of 12 months may be granted for members who achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition when either of the following is met: Reduction in body surface area (BSA) affected from baseline OR Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).; The policy states that continuation requests require chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.</t>
+  </si>
+  <si>
+    <t>Initial criteria has been met; The member has had a positive response to therapy</t>
+  </si>
+  <si>
+    <t>The patient has been previously approved for the requested agent through the plan’s Prior Authorization process; The patient has had clinical benefit with the requested agent; If the client has preferred agents, then the requested agent is a preferred agent OR the patient has tried and had an inadequate response/intolerance to the specified number of preferred agents; The prescriber is a specialist in the area of the patient’s diagnosis (e.g., rheumatologist for JIA, PsA, RA; gastroenterologist for CD, UC; dermatologist for PS), or the prescriber has consulted with a specialist in the area of the patient’s diagnosis; The patient will NOT be using the requested agent in combination with another immunomodulatory agent (e.g., TNF inhibitors, JAK inhibitors, IL-4 inhibitors)</t>
+  </si>
+  <si>
+    <t>The member is using the requested medication for moderate to severe plaque psoriasis and achieves or maintains a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; Reduction in body surface area (BSA) affected from baseline.; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).; Chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.</t>
+  </si>
+  <si>
+    <t>Chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.; Achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition when either of the following is met: Reduction in body surface area (BSA) affected from baseline; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain)</t>
+  </si>
+  <si>
+    <t>The policy states that subsequent approvals may be limited to 3 to 6 months for the following reasons: inadequate response to treatment, inconsistent pattern of medication adherence, safety concern, or off-label dosing.; The policy states that in general, if renewal requirements are satisfied, subsequent approvals of 12 months duration are contingent on demonstrated response as evident in the medical records.; The policy states that for Plaque psoriasis, continuation coverage is limited to Members who demonstrate clearing of 50% or greater of affected body surface area of plaque psoriasis.</t>
+  </si>
+  <si>
+    <t>The policy states: 'For continuation requests (all diagnoses): Member has benefited with use of this medication.'</t>
+  </si>
+  <si>
+    <t>Initial criteria met; The member has had a positive response to therapy; Documentation of clinical justification to continue therapy with the requested medication</t>
+  </si>
+  <si>
+    <t>Member has benefited with use of this medication.</t>
+  </si>
+  <si>
+    <t>The document states: 'Renewal PA requests for non-preferred cytokine and CAM antagonist drugs must include supporting clinical information and copies of the member's current medical records demonstrating that the member had a significant reduction in symptoms compared to their baseline prior to the initiation of the non-preferred cytokine and CAM antagonist drug.'; The document states: 'All renewal PA requests require the member to be adherent with the prescribed treatment regimen.'</t>
+  </si>
+  <si>
+    <t>The policy states that renewal PA requests for non-preferred cytokine and CAM antagonist drugs must include supporting clinical information and copies of the member's current medical records demonstrating that the member had a significant reduction in symptoms compared to their baseline prior to the initiation of the non-preferred cytokine and CAM antagonist drug.; The policy states that all renewal PA requests require the member to be adherent with the prescribed treatment regimen.</t>
+  </si>
+  <si>
+    <t>Not used in combination with another Cytokine and CAM medication; Documentation is submitted demonstrating disease stability or a positive clinical response (e.g., improvement in BSA, PASI, Psoriasis PGA, itch numeric rating scale); For Non-Preferred ustekinumab biosimilars and brand name ustekinumab (Stelara), patient has met all criteria listed in Non-Clinical Policy No. 0001 (NC-001)</t>
+  </si>
+  <si>
+    <t>Not used in combination with another Cytokine and CAM medication; Documentation is submitted demonstrating disease stability or a positive clinical response (e.g., improvement in BSA, PASI, Psoriasis PGA, itch numeric rating scale)</t>
+  </si>
+  <si>
+    <t>The policy states: 'Member is ≥18 years of age'; The policy states: 'Prescribed by or in consultation with a dermatologist'; The policy states: 'Diagnosis of plaque psoriasis'; The policy states: 'Documentation of positive clinical response to Tremfya therapy (e.g., labs, sign/symptom reduction, no disease progression, no significant toxicity)'; The policy states: 'Member is not on concurrent treatment with a TNF-inhibitor, biologic response modifier or other non-biologic agent'</t>
+  </si>
+  <si>
+    <t>The policy states that for continuation of therapy, the prescriber must provide documentation of all of the following: Member is ≥6 years of age; The policy states that for continuation of therapy, the prescriber must provide documentation of all of the following: Prescribed by or in consultation with a dermatologist; The policy states that for continuation of therapy, the prescriber must provide documentation of all of the following: Diagnosis of plaque psoriasis; The policy states that for continuation of therapy, the prescriber must provide documentation of all of the following: Member must have demonstrated a clinical response to therapy (i.e. reduction in body surface area involvement or improvement in PASI score); The policy states that for continuation of therapy, the prescriber must provide documentation of all of the following: Member is not on concurrent treatment with a TNF-inhibitor, biologic response modifier or other non-biologic agent</t>
+  </si>
+  <si>
+    <t>The policy states that for continuation of therapy, the prescriber must provide documentation that the member is ≥6 years of age.; The policy states that for continuation of therapy, the prescriber must provide documentation that the drug is prescribed by or in consultation with a dermatologist.; The policy states that for continuation of therapy, the prescriber must provide documentation of a diagnosis of plaque psoriasis.; The policy states that for continuation of therapy, the prescriber must provide documentation that the member must have demonstrated a clinical response to therapy (i.e. reduction in body surface area involvement or improvement in PASI score).; The policy states that for continuation of therapy, the prescriber must provide documentation that the member is not on concurrent treatment with a TNF-inhibitor, biologic response modifier or other non-biologic agent.</t>
+  </si>
+  <si>
+    <t>The policy states that extension requests will be approved up to 12 months if the member has a continued benefit to therapy.; The policy states that extension requests where the ustekinumab did not have the full desired effect or considered a clinical failure will require clinical rationale for continuing.</t>
+  </si>
+  <si>
+    <t>The member must achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; Reduction in body surface area (BSA) affected from baseline.; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).; Submission of chart notes or medical record documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms.</t>
+  </si>
+  <si>
+    <t>The policy states that for continuation of therapy, the member must achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; The policy states that documentation of decreased body surface area (BSA) affected and/or improvement in signs and symptoms is required.; The policy states that one of the following must be met: Reduction in body surface area (BSA) affected from baseline or improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).</t>
+  </si>
+  <si>
+    <t>The member was previously authorized by HMSA/HMSA’s Pharmacy Benefit Manager for the requested drug.; Achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; Reduction in body surface area (BSA) affected from baseline.; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).</t>
+  </si>
+  <si>
+    <t>Documentation of positive clinical response; Prescriber attestation that the patient or caregiver are not able to be trained or are physically unable to administer ustekinumab FDA labeled for self-administration; prescriber must submit explanation; Ustekinumab is initiated and titrated according to US Food and Drug Administration labeled dosing for plaque psoriasis; Patient is not receiving ustekinumab in combination with a targeted immunomodulator</t>
+  </si>
+  <si>
+    <t>The patient has been previously approved for the requested agent through the plan’s Prior Authorization process.; The request is NOT for use of Olumiant or Actemra in the treatment of coronavirus disease 2019 (COVID-19) in hospitalized adults requiring supplemental oxygen, non-invasive or invasive mechanical ventilation, or extracorporeal membrane oxygenation (ECMO).</t>
+  </si>
+  <si>
+    <t>A letter of medical necessity with chart notes demonstrating therapeutic benefit.; Baseline and current PASI score (or equivalent, for Ps).; Documentation of tolerance and absence of adverse events.</t>
+  </si>
+  <si>
+    <t>Patient demonstrates positive clinical response to therapy as evidenced by ONE of the following: Reduction in the body surface area (BSA) involvement from baseline; Improvement in symptoms (e.g., pruritus, inflammation) from baseline</t>
+  </si>
+  <si>
+    <t>The member must achieve or maintain a positive clinical response as evidenced by low disease activity or improvement in signs and symptoms of the condition.; Reduction in body surface area (BSA) affected from baseline.; Improvement in signs and symptoms from baseline (e.g., itching, redness, flaking, scaling, burning, cracking, pain).</t>
+  </si>
+  <si>
+    <t>Has the patient been adherent to both biologic and DMARD therapy (if DMARD therapy has been prescribed in conjunction with the biologic therapy)?; Has the patient’s condition improved as assessed by the prescribing provider and provider attests to patient’s improvement.</t>
+  </si>
+  <si>
+    <t>Patient continues to meet the universal and other indication-specific relevant criteria identified in section III; Duration of authorization has not been exceeded; Absence of unacceptable toxicity from the drug; Disease response as indicated by improvement in signs and symptoms compared to baseline such as redness, thickness, scaliness, and/or the amount of surface area involvement (a total BSA involvement ≤ 1%), and/or an improvement on a disease activity scoring tool [e.g., Psoriasis Area and Severity Index (PASI) score ≤ 3, physician’s global assessment (PGA) score ≤ 1, etc.]</t>
+  </si>
+  <si>
+    <t>The patient has been previously approved for the requested agent through the plan’s Prior Authorization process; The patient has had clinical benefit with the requested agent; If the client has preferred agents, then ONE of the following (reference preferred agents table): The requested agent is a preferred agent OR The patient has tried and had an inadequate response to THREE preferred agents after at least a 3-month trial per agent (medical records required) OR The patient has an intolerance or hypersensitivity to THREE of the preferred agents that is not expected to occur with the requested agent (medical records required) OR The patient has an FDA labeled contraindication to ALL of the preferred agents that is not expected to occur with the requested agent (medical records required) OR BOTH of the following (medical records required): ALL of the preferred agents are not clinically appropriate for the patient AND The prescriber has provided a complete list of previously tried agents</t>
+  </si>
+  <si>
+    <t>The individual has been previously approved for therapy through BCBSMS PA process; The individual has shown clinical improvement (i.e. slowing of disease progression or decrease in symptom severity and/or frequency); The individual does not have any FDA-labeled contraindication(s) to therapy with the requested agent; The individual is not currently being treated with another biologic immunomodulatory agent (i.e., TNF-inhibitor, IL-inhibitor, anti IgE antibody, etc.) or Otezla; The prescribed dosage is within the program quantity limits based on FDA-approved labeled dosage</t>
+  </si>
+  <si>
+    <t>The policy states: 'Applies if the patient has had a response, as determined by the prescriber. The patient may not have a full response, but there should have been a recent or past response to Enbrel.'</t>
+  </si>
+  <si>
+    <t>Patient continues to meet the universal and other indication-specific relevant criteria identified in section III; Duration of authorization has not been exceeded; Absence of unacceptable toxicity from the drug</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,13 +906,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +958,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +992,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +1027,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +1203,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,54 +1271,3721 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2" t="s">
+        <v>173</v>
+      </c>
+      <c r="N2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K3" t="s">
+        <v>199</v>
+      </c>
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" t="s">
+        <v>173</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="E2">
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
+        <v>190</v>
+      </c>
+      <c r="K5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" t="s">
+        <v>200</v>
+      </c>
+      <c r="M5" t="s">
+        <v>174</v>
+      </c>
+      <c r="N5" t="s">
+        <v>205</v>
+      </c>
+      <c r="O5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K6" t="s">
+        <v>200</v>
+      </c>
+      <c r="L6" t="s">
+        <v>200</v>
+      </c>
+      <c r="M6" t="s">
+        <v>174</v>
+      </c>
+      <c r="N6" t="s">
+        <v>206</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I7" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" t="s">
+        <v>200</v>
+      </c>
+      <c r="L7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M7" t="s">
+        <v>174</v>
+      </c>
+      <c r="N7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8" t="s">
+        <v>201</v>
+      </c>
+      <c r="L8" t="s">
+        <v>200</v>
+      </c>
+      <c r="M8" t="s">
+        <v>174</v>
+      </c>
+      <c r="N8" t="s">
+        <v>208</v>
+      </c>
+      <c r="O8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" t="s">
+        <v>178</v>
+      </c>
+      <c r="J9" t="s">
+        <v>191</v>
+      </c>
+      <c r="K9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L9" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" t="s">
+        <v>173</v>
+      </c>
+      <c r="N9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" t="s">
+        <v>200</v>
+      </c>
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M10" t="s">
+        <v>173</v>
+      </c>
+      <c r="N10" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" t="s">
+        <v>191</v>
+      </c>
+      <c r="K11" t="s">
+        <v>200</v>
+      </c>
+      <c r="L11" t="s">
+        <v>199</v>
+      </c>
+      <c r="M11" t="s">
+        <v>174</v>
+      </c>
+      <c r="N11" t="s">
+        <v>209</v>
+      </c>
+      <c r="O11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" t="s">
+        <v>201</v>
+      </c>
+      <c r="L12" t="s">
+        <v>200</v>
+      </c>
+      <c r="M12" t="s">
+        <v>174</v>
+      </c>
+      <c r="N12" t="s">
+        <v>210</v>
+      </c>
+      <c r="O12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" t="s">
+        <v>103</v>
+      </c>
+      <c r="J13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" t="s">
+        <v>199</v>
+      </c>
+      <c r="M13" t="s">
+        <v>174</v>
+      </c>
+      <c r="N13" t="s">
+        <v>211</v>
+      </c>
+      <c r="O13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" t="s">
+        <v>200</v>
+      </c>
+      <c r="M14" t="s">
+        <v>174</v>
+      </c>
+      <c r="N14" t="s">
+        <v>212</v>
+      </c>
+      <c r="O14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" t="s">
+        <v>201</v>
+      </c>
+      <c r="L15" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" t="s">
+        <v>174</v>
+      </c>
+      <c r="N15" t="s">
+        <v>213</v>
+      </c>
+      <c r="O15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" t="s">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" t="s">
+        <v>174</v>
+      </c>
+      <c r="N16" t="s">
+        <v>213</v>
+      </c>
+      <c r="O16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G17" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17" t="s">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s">
+        <v>174</v>
+      </c>
+      <c r="N17" t="s">
+        <v>214</v>
+      </c>
+      <c r="O17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" t="s">
+        <v>173</v>
+      </c>
+      <c r="I18" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" t="s">
+        <v>190</v>
+      </c>
+      <c r="K18" t="s">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s">
+        <v>174</v>
+      </c>
+      <c r="N18" t="s">
+        <v>215</v>
+      </c>
+      <c r="O18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" t="s">
+        <v>173</v>
+      </c>
+      <c r="I19" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" t="s">
+        <v>199</v>
+      </c>
+      <c r="L19" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19" t="s">
+        <v>173</v>
+      </c>
+      <c r="N19" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" t="s">
+        <v>103</v>
+      </c>
+      <c r="J20" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" t="s">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N20" t="s">
+        <v>216</v>
+      </c>
+      <c r="O20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I21" t="s">
+        <v>103</v>
+      </c>
+      <c r="J21" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" t="s">
+        <v>200</v>
+      </c>
+      <c r="L21" t="s">
+        <v>200</v>
+      </c>
+      <c r="M21" t="s">
+        <v>174</v>
+      </c>
+      <c r="N21" t="s">
+        <v>217</v>
+      </c>
+      <c r="O21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" t="s">
+        <v>173</v>
+      </c>
+      <c r="I22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" t="s">
+        <v>199</v>
+      </c>
+      <c r="L22" t="s">
+        <v>200</v>
+      </c>
+      <c r="M22" t="s">
+        <v>174</v>
+      </c>
+      <c r="N22" t="s">
+        <v>218</v>
+      </c>
+      <c r="O22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" t="s">
+        <v>103</v>
+      </c>
+      <c r="J23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" t="s">
+        <v>199</v>
+      </c>
+      <c r="L23" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" t="s">
+        <v>173</v>
+      </c>
+      <c r="N23" t="s">
+        <v>103</v>
+      </c>
+      <c r="O23">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" t="s">
+        <v>103</v>
+      </c>
+      <c r="J24" t="s">
+        <v>191</v>
+      </c>
+      <c r="K24" t="s">
+        <v>201</v>
+      </c>
+      <c r="L24" t="s">
+        <v>200</v>
+      </c>
+      <c r="M24" t="s">
+        <v>174</v>
+      </c>
+      <c r="N24" t="s">
+        <v>219</v>
+      </c>
+      <c r="O24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" t="s">
+        <v>201</v>
+      </c>
+      <c r="L25" t="s">
+        <v>200</v>
+      </c>
+      <c r="M25" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" t="s">
+        <v>220</v>
+      </c>
+      <c r="O25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" t="s">
+        <v>103</v>
+      </c>
+      <c r="J26" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" t="s">
+        <v>201</v>
+      </c>
+      <c r="L26" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" t="s">
+        <v>174</v>
+      </c>
+      <c r="N26" t="s">
+        <v>219</v>
+      </c>
+      <c r="O26">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27" t="s">
+        <v>103</v>
+      </c>
+      <c r="K27" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" t="s">
+        <v>174</v>
+      </c>
+      <c r="N27" t="s">
+        <v>221</v>
+      </c>
+      <c r="O27">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" t="s">
+        <v>103</v>
+      </c>
+      <c r="J28" t="s">
+        <v>103</v>
+      </c>
+      <c r="K28" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" t="s">
+        <v>103</v>
+      </c>
+      <c r="M28" t="s">
+        <v>173</v>
+      </c>
+      <c r="N28" t="s">
+        <v>103</v>
+      </c>
+      <c r="O28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>173</v>
+      </c>
+      <c r="H29" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J29" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" t="s">
+        <v>201</v>
+      </c>
+      <c r="L29" t="s">
+        <v>200</v>
+      </c>
+      <c r="M29" t="s">
+        <v>174</v>
+      </c>
+      <c r="N29" t="s">
+        <v>222</v>
+      </c>
+      <c r="O29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" t="s">
+        <v>103</v>
+      </c>
+      <c r="J30" t="s">
+        <v>103</v>
+      </c>
+      <c r="K30" t="s">
+        <v>201</v>
+      </c>
+      <c r="L30" t="s">
+        <v>200</v>
+      </c>
+      <c r="M30" t="s">
+        <v>174</v>
+      </c>
+      <c r="N30" t="s">
+        <v>223</v>
+      </c>
+      <c r="O30">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" t="s">
+        <v>103</v>
+      </c>
+      <c r="J31" t="s">
+        <v>103</v>
+      </c>
+      <c r="K31" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" t="s">
+        <v>174</v>
+      </c>
+      <c r="N31" t="s">
+        <v>224</v>
+      </c>
+      <c r="O31">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" t="s">
+        <v>103</v>
+      </c>
+      <c r="K32" t="s">
+        <v>199</v>
+      </c>
+      <c r="L32" t="s">
+        <v>103</v>
+      </c>
+      <c r="M32" t="s">
+        <v>173</v>
+      </c>
+      <c r="N32" t="s">
+        <v>103</v>
+      </c>
+      <c r="O32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" t="s">
+        <v>103</v>
+      </c>
+      <c r="J33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33" t="s">
+        <v>200</v>
+      </c>
+      <c r="M33" t="s">
+        <v>174</v>
+      </c>
+      <c r="N33" t="s">
+        <v>225</v>
+      </c>
+      <c r="O33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" t="s">
+        <v>173</v>
+      </c>
+      <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" t="s">
+        <v>203</v>
+      </c>
+      <c r="L34" t="s">
+        <v>200</v>
+      </c>
+      <c r="M34" t="s">
+        <v>174</v>
+      </c>
+      <c r="N34" t="s">
+        <v>226</v>
+      </c>
+      <c r="O34">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" t="s">
+        <v>173</v>
+      </c>
+      <c r="I35" t="s">
+        <v>181</v>
+      </c>
+      <c r="J35" t="s">
+        <v>103</v>
+      </c>
+      <c r="K35" t="s">
+        <v>203</v>
+      </c>
+      <c r="L35" t="s">
+        <v>200</v>
+      </c>
+      <c r="M35" t="s">
+        <v>174</v>
+      </c>
+      <c r="N35" t="s">
+        <v>226</v>
+      </c>
+      <c r="O35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" t="s">
+        <v>103</v>
+      </c>
+      <c r="J36" t="s">
+        <v>103</v>
+      </c>
+      <c r="K36" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36" t="s">
+        <v>200</v>
+      </c>
+      <c r="M36" t="s">
+        <v>174</v>
+      </c>
+      <c r="N36" t="s">
+        <v>227</v>
+      </c>
+      <c r="O36">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" t="s">
+        <v>174</v>
+      </c>
+      <c r="I37" t="s">
+        <v>103</v>
+      </c>
+      <c r="J37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" t="s">
+        <v>199</v>
+      </c>
+      <c r="L37" t="s">
+        <v>103</v>
+      </c>
+      <c r="M37" t="s">
+        <v>174</v>
+      </c>
+      <c r="N37" t="s">
+        <v>228</v>
+      </c>
+      <c r="O37">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" t="s">
+        <v>182</v>
+      </c>
+      <c r="J38" t="s">
+        <v>103</v>
+      </c>
+      <c r="K38" t="s">
+        <v>201</v>
+      </c>
+      <c r="L38" t="s">
+        <v>201</v>
+      </c>
+      <c r="M38" t="s">
+        <v>174</v>
+      </c>
+      <c r="N38" t="s">
+        <v>229</v>
+      </c>
+      <c r="O38">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>173</v>
+      </c>
+      <c r="H39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" t="s">
+        <v>103</v>
+      </c>
+      <c r="J39" t="s">
+        <v>190</v>
+      </c>
+      <c r="K39" t="s">
+        <v>200</v>
+      </c>
+      <c r="L39" t="s">
+        <v>200</v>
+      </c>
+      <c r="M39" t="s">
+        <v>174</v>
+      </c>
+      <c r="N39" t="s">
+        <v>230</v>
+      </c>
+      <c r="O39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" t="s">
+        <v>103</v>
+      </c>
+      <c r="J40" t="s">
+        <v>192</v>
+      </c>
+      <c r="K40" t="s">
+        <v>199</v>
+      </c>
+      <c r="L40" t="s">
+        <v>103</v>
+      </c>
+      <c r="M40" t="s">
+        <v>173</v>
+      </c>
+      <c r="N40" t="s">
+        <v>103</v>
+      </c>
+      <c r="O40">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" t="s">
+        <v>174</v>
+      </c>
+      <c r="I41" t="s">
+        <v>103</v>
+      </c>
+      <c r="J41" t="s">
+        <v>192</v>
+      </c>
+      <c r="K41" t="s">
+        <v>199</v>
+      </c>
+      <c r="L41" t="s">
+        <v>103</v>
+      </c>
+      <c r="M41" t="s">
+        <v>173</v>
+      </c>
+      <c r="N41" t="s">
+        <v>103</v>
+      </c>
+      <c r="O41">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" t="s">
+        <v>103</v>
+      </c>
+      <c r="J42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K42" t="s">
+        <v>200</v>
+      </c>
+      <c r="L42" t="s">
+        <v>199</v>
+      </c>
+      <c r="M42" t="s">
+        <v>174</v>
+      </c>
+      <c r="N42" t="s">
+        <v>231</v>
+      </c>
+      <c r="O42">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" t="s">
+        <v>103</v>
+      </c>
+      <c r="J43" t="s">
+        <v>190</v>
+      </c>
+      <c r="K43" t="s">
+        <v>200</v>
+      </c>
+      <c r="L43" t="s">
+        <v>200</v>
+      </c>
+      <c r="M43" t="s">
+        <v>174</v>
+      </c>
+      <c r="N43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O43">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" t="s">
+        <v>173</v>
+      </c>
+      <c r="I44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J44" t="s">
+        <v>190</v>
+      </c>
+      <c r="K44" t="s">
+        <v>201</v>
+      </c>
+      <c r="L44" t="s">
+        <v>200</v>
+      </c>
+      <c r="M44" t="s">
+        <v>174</v>
+      </c>
+      <c r="N44" t="s">
+        <v>233</v>
+      </c>
+      <c r="O44">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" t="s">
+        <v>173</v>
+      </c>
+      <c r="H45" t="s">
+        <v>174</v>
+      </c>
+      <c r="I45" t="s">
+        <v>103</v>
+      </c>
+      <c r="J45" t="s">
+        <v>193</v>
+      </c>
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45" t="s">
+        <v>199</v>
+      </c>
+      <c r="M45" t="s">
+        <v>174</v>
+      </c>
+      <c r="N45" t="s">
+        <v>234</v>
+      </c>
+      <c r="O45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" t="s">
+        <v>174</v>
+      </c>
+      <c r="I46" t="s">
+        <v>183</v>
+      </c>
+      <c r="J46" t="s">
+        <v>190</v>
+      </c>
+      <c r="K46" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46" t="s">
+        <v>200</v>
+      </c>
+      <c r="M46" t="s">
+        <v>174</v>
+      </c>
+      <c r="N46" t="s">
+        <v>235</v>
+      </c>
+      <c r="O46">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" t="s">
+        <v>184</v>
+      </c>
+      <c r="J47" t="s">
+        <v>190</v>
+      </c>
+      <c r="K47" t="s">
+        <v>200</v>
+      </c>
+      <c r="L47" t="s">
+        <v>200</v>
+      </c>
+      <c r="M47" t="s">
+        <v>174</v>
+      </c>
+      <c r="N47" t="s">
+        <v>236</v>
+      </c>
+      <c r="O47">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" t="s">
+        <v>173</v>
+      </c>
+      <c r="I48" t="s">
+        <v>103</v>
+      </c>
+      <c r="J48" t="s">
+        <v>190</v>
+      </c>
+      <c r="K48" t="s">
+        <v>103</v>
+      </c>
+      <c r="L48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M48" t="s">
+        <v>173</v>
+      </c>
+      <c r="N48" t="s">
+        <v>103</v>
+      </c>
+      <c r="O48">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I49" t="s">
+        <v>103</v>
+      </c>
+      <c r="J49" t="s">
+        <v>103</v>
+      </c>
+      <c r="K49" t="s">
+        <v>199</v>
+      </c>
+      <c r="L49" t="s">
+        <v>103</v>
+      </c>
+      <c r="M49" t="s">
+        <v>173</v>
+      </c>
+      <c r="N49" t="s">
+        <v>103</v>
+      </c>
+      <c r="O49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" t="s">
+        <v>173</v>
+      </c>
+      <c r="I50" t="s">
+        <v>103</v>
+      </c>
+      <c r="J50" t="s">
+        <v>103</v>
+      </c>
+      <c r="K50" t="s">
+        <v>199</v>
+      </c>
+      <c r="L50" t="s">
+        <v>103</v>
+      </c>
+      <c r="M50" t="s">
+        <v>173</v>
+      </c>
+      <c r="N50" t="s">
+        <v>103</v>
+      </c>
+      <c r="O50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" t="s">
+        <v>103</v>
+      </c>
+      <c r="F51" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" t="s">
+        <v>103</v>
+      </c>
+      <c r="J51" t="s">
+        <v>194</v>
+      </c>
+      <c r="K51" t="s">
+        <v>199</v>
+      </c>
+      <c r="L51" t="s">
+        <v>103</v>
+      </c>
+      <c r="M51" t="s">
+        <v>173</v>
+      </c>
+      <c r="N51" t="s">
+        <v>103</v>
+      </c>
+      <c r="O51">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" t="s">
+        <v>150</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" t="s">
+        <v>174</v>
+      </c>
+      <c r="I52" t="s">
+        <v>103</v>
+      </c>
+      <c r="J52" t="s">
+        <v>103</v>
+      </c>
+      <c r="K52" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" t="s">
+        <v>200</v>
+      </c>
+      <c r="M52" t="s">
+        <v>174</v>
+      </c>
+      <c r="N52" t="s">
+        <v>103</v>
+      </c>
+      <c r="O52">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>173</v>
+      </c>
+      <c r="H53" t="s">
+        <v>174</v>
+      </c>
+      <c r="I53" t="s">
+        <v>103</v>
+      </c>
+      <c r="J53" t="s">
+        <v>195</v>
+      </c>
+      <c r="K53" t="s">
+        <v>201</v>
+      </c>
+      <c r="L53" t="s">
+        <v>199</v>
+      </c>
+      <c r="M53" t="s">
+        <v>174</v>
+      </c>
+      <c r="N53" t="s">
+        <v>237</v>
+      </c>
+      <c r="O53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>173</v>
+      </c>
+      <c r="H54" t="s">
+        <v>173</v>
+      </c>
+      <c r="I54" t="s">
+        <v>103</v>
+      </c>
+      <c r="J54" t="s">
+        <v>190</v>
+      </c>
+      <c r="K54" t="s">
+        <v>200</v>
+      </c>
+      <c r="L54" t="s">
+        <v>200</v>
+      </c>
+      <c r="M54" t="s">
+        <v>174</v>
+      </c>
+      <c r="N54" t="s">
+        <v>238</v>
+      </c>
+      <c r="O54">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>173</v>
+      </c>
+      <c r="H55" t="s">
+        <v>173</v>
+      </c>
+      <c r="I55" t="s">
+        <v>103</v>
+      </c>
+      <c r="J55" t="s">
+        <v>190</v>
+      </c>
+      <c r="K55" t="s">
+        <v>201</v>
+      </c>
+      <c r="L55" t="s">
+        <v>200</v>
+      </c>
+      <c r="M55" t="s">
+        <v>174</v>
+      </c>
+      <c r="N55" t="s">
+        <v>239</v>
+      </c>
+      <c r="O55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" t="s">
+        <v>103</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" t="s">
+        <v>173</v>
+      </c>
+      <c r="I56" t="s">
+        <v>103</v>
+      </c>
+      <c r="J56" t="s">
+        <v>190</v>
+      </c>
+      <c r="K56" t="s">
+        <v>200</v>
+      </c>
+      <c r="L56" t="s">
+        <v>200</v>
+      </c>
+      <c r="M56" t="s">
+        <v>174</v>
+      </c>
+      <c r="N56" t="s">
+        <v>240</v>
+      </c>
+      <c r="O56">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" t="s">
+        <v>103</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>173</v>
+      </c>
+      <c r="H57" t="s">
+        <v>173</v>
+      </c>
+      <c r="I57" t="s">
+        <v>103</v>
+      </c>
+      <c r="J57" t="s">
+        <v>190</v>
+      </c>
+      <c r="K57" t="s">
+        <v>200</v>
+      </c>
+      <c r="L57" t="s">
+        <v>200</v>
+      </c>
+      <c r="M57" t="s">
+        <v>174</v>
+      </c>
+      <c r="N57" t="s">
+        <v>240</v>
+      </c>
+      <c r="O57">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" t="s">
+        <v>103</v>
+      </c>
+      <c r="H58" t="s">
+        <v>173</v>
+      </c>
+      <c r="I58" t="s">
+        <v>103</v>
+      </c>
+      <c r="J58" t="s">
+        <v>190</v>
+      </c>
+      <c r="K58" t="s">
+        <v>201</v>
+      </c>
+      <c r="L58" t="s">
+        <v>200</v>
+      </c>
+      <c r="M58" t="s">
+        <v>174</v>
+      </c>
+      <c r="N58" t="s">
+        <v>241</v>
+      </c>
+      <c r="O58">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" t="s">
+        <v>103</v>
+      </c>
+      <c r="E59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" t="s">
+        <v>103</v>
+      </c>
+      <c r="H59" t="s">
+        <v>173</v>
+      </c>
+      <c r="I59" t="s">
+        <v>103</v>
+      </c>
+      <c r="J59" t="s">
+        <v>190</v>
+      </c>
+      <c r="K59" t="s">
+        <v>201</v>
+      </c>
+      <c r="L59" t="s">
+        <v>200</v>
+      </c>
+      <c r="M59" t="s">
+        <v>174</v>
+      </c>
+      <c r="N59" t="s">
+        <v>242</v>
+      </c>
+      <c r="O59">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" t="s">
+        <v>155</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>173</v>
+      </c>
+      <c r="H60" t="s">
+        <v>173</v>
+      </c>
+      <c r="I60" t="s">
+        <v>103</v>
+      </c>
+      <c r="J60" t="s">
+        <v>190</v>
+      </c>
+      <c r="K60" t="s">
+        <v>200</v>
+      </c>
+      <c r="L60" t="s">
+        <v>200</v>
+      </c>
+      <c r="M60" t="s">
+        <v>174</v>
+      </c>
+      <c r="N60" t="s">
+        <v>243</v>
+      </c>
+      <c r="O60">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>87</v>
+      </c>
+      <c r="C61" t="s">
+        <v>101</v>
+      </c>
+      <c r="D61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>173</v>
+      </c>
+      <c r="H61" t="s">
+        <v>173</v>
+      </c>
+      <c r="I61" t="s">
+        <v>103</v>
+      </c>
+      <c r="J61" t="s">
+        <v>190</v>
+      </c>
+      <c r="K61" t="s">
+        <v>200</v>
+      </c>
+      <c r="L61" t="s">
+        <v>200</v>
+      </c>
+      <c r="M61" t="s">
+        <v>174</v>
+      </c>
+      <c r="N61" t="s">
+        <v>244</v>
+      </c>
+      <c r="O61">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" t="s">
+        <v>157</v>
+      </c>
+      <c r="E62" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>173</v>
+      </c>
+      <c r="H62" t="s">
+        <v>173</v>
+      </c>
+      <c r="I62" t="s">
+        <v>185</v>
+      </c>
+      <c r="J62" t="s">
+        <v>190</v>
+      </c>
+      <c r="K62" t="s">
+        <v>199</v>
+      </c>
+      <c r="L62" t="s">
+        <v>200</v>
+      </c>
+      <c r="M62" t="s">
+        <v>174</v>
+      </c>
+      <c r="N62" t="s">
+        <v>245</v>
+      </c>
+      <c r="O62">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" t="s">
+        <v>157</v>
+      </c>
+      <c r="E63" t="s">
+        <v>103</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>173</v>
+      </c>
+      <c r="H63" t="s">
+        <v>173</v>
+      </c>
+      <c r="I63" t="s">
+        <v>186</v>
+      </c>
+      <c r="J63" t="s">
+        <v>190</v>
+      </c>
+      <c r="K63" t="s">
+        <v>201</v>
+      </c>
+      <c r="L63" t="s">
+        <v>200</v>
+      </c>
+      <c r="M63" t="s">
+        <v>174</v>
+      </c>
+      <c r="N63" t="s">
+        <v>246</v>
+      </c>
+      <c r="O63">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" t="s">
+        <v>157</v>
+      </c>
+      <c r="E64" t="s">
+        <v>103</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>173</v>
+      </c>
+      <c r="H64" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" t="s">
+        <v>186</v>
+      </c>
+      <c r="J64" t="s">
+        <v>190</v>
+      </c>
+      <c r="K64" t="s">
+        <v>201</v>
+      </c>
+      <c r="L64" t="s">
+        <v>200</v>
+      </c>
+      <c r="M64" t="s">
+        <v>174</v>
+      </c>
+      <c r="N64" t="s">
+        <v>247</v>
+      </c>
+      <c r="O64">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" t="s">
+        <v>158</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>103</v>
+      </c>
+      <c r="G65" t="s">
+        <v>173</v>
+      </c>
+      <c r="H65" t="s">
+        <v>173</v>
+      </c>
+      <c r="I65" t="s">
+        <v>103</v>
+      </c>
+      <c r="J65" t="s">
+        <v>196</v>
+      </c>
+      <c r="K65" t="s">
+        <v>201</v>
+      </c>
+      <c r="L65" t="s">
+        <v>200</v>
+      </c>
+      <c r="M65" t="s">
+        <v>174</v>
+      </c>
+      <c r="N65" t="s">
+        <v>248</v>
+      </c>
+      <c r="O65">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" t="s">
+        <v>159</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="s">
+        <v>173</v>
+      </c>
+      <c r="H66" t="s">
+        <v>174</v>
+      </c>
+      <c r="I66" t="s">
+        <v>187</v>
+      </c>
+      <c r="J66" t="s">
+        <v>190</v>
+      </c>
+      <c r="K66" t="s">
+        <v>200</v>
+      </c>
+      <c r="L66" t="s">
+        <v>200</v>
+      </c>
+      <c r="M66" t="s">
+        <v>174</v>
+      </c>
+      <c r="N66" t="s">
+        <v>249</v>
+      </c>
+      <c r="O66">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>173</v>
+      </c>
+      <c r="H67" t="s">
+        <v>174</v>
+      </c>
+      <c r="I67" t="s">
+        <v>184</v>
+      </c>
+      <c r="J67" t="s">
+        <v>190</v>
+      </c>
+      <c r="K67" t="s">
+        <v>200</v>
+      </c>
+      <c r="L67" t="s">
+        <v>200</v>
+      </c>
+      <c r="M67" t="s">
+        <v>174</v>
+      </c>
+      <c r="N67" t="s">
+        <v>250</v>
+      </c>
+      <c r="O67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68" t="s">
+        <v>161</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>173</v>
+      </c>
+      <c r="H68" t="s">
+        <v>174</v>
+      </c>
+      <c r="I68" t="s">
+        <v>103</v>
+      </c>
+      <c r="J68" t="s">
+        <v>197</v>
+      </c>
+      <c r="K68" t="s">
+        <v>200</v>
+      </c>
+      <c r="L68" t="s">
+        <v>200</v>
+      </c>
+      <c r="M68" t="s">
+        <v>174</v>
+      </c>
+      <c r="N68" t="s">
+        <v>251</v>
+      </c>
+      <c r="O68">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>173</v>
+      </c>
+      <c r="H69" t="s">
+        <v>173</v>
+      </c>
+      <c r="I69" t="s">
+        <v>103</v>
+      </c>
+      <c r="J69" t="s">
+        <v>190</v>
+      </c>
+      <c r="K69" t="s">
+        <v>200</v>
+      </c>
+      <c r="L69" t="s">
+        <v>200</v>
+      </c>
+      <c r="M69" t="s">
+        <v>174</v>
+      </c>
+      <c r="N69" t="s">
+        <v>252</v>
+      </c>
+      <c r="O69">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>173</v>
+      </c>
+      <c r="H70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" t="s">
+        <v>103</v>
+      </c>
+      <c r="J70" t="s">
+        <v>190</v>
+      </c>
+      <c r="K70" t="s">
+        <v>203</v>
+      </c>
+      <c r="L70" t="s">
+        <v>200</v>
+      </c>
+      <c r="M70" t="s">
+        <v>174</v>
+      </c>
+      <c r="N70" t="s">
+        <v>253</v>
+      </c>
+      <c r="O70">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" t="s">
+        <v>85</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" t="s">
+        <v>164</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>173</v>
+      </c>
+      <c r="H71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I71" t="s">
+        <v>188</v>
+      </c>
+      <c r="J71" t="s">
+        <v>103</v>
+      </c>
+      <c r="K71" t="s">
+        <v>204</v>
+      </c>
+      <c r="L71" t="s">
+        <v>200</v>
+      </c>
+      <c r="M71" t="s">
+        <v>174</v>
+      </c>
+      <c r="N71" t="s">
+        <v>254</v>
+      </c>
+      <c r="O71">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" t="s">
+        <v>103</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>173</v>
+      </c>
+      <c r="H72" t="s">
+        <v>173</v>
+      </c>
+      <c r="I72" t="s">
+        <v>103</v>
+      </c>
+      <c r="J72" t="s">
+        <v>190</v>
+      </c>
+      <c r="K72" t="s">
+        <v>201</v>
+      </c>
+      <c r="L72" t="s">
+        <v>200</v>
+      </c>
+      <c r="M72" t="s">
+        <v>174</v>
+      </c>
+      <c r="N72" t="s">
+        <v>255</v>
+      </c>
+      <c r="O72">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73" t="s">
+        <v>103</v>
+      </c>
+      <c r="D73" t="s">
+        <v>166</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" t="s">
+        <v>173</v>
+      </c>
+      <c r="H73" t="s">
+        <v>173</v>
+      </c>
+      <c r="I73" t="s">
+        <v>103</v>
+      </c>
+      <c r="J73" t="s">
+        <v>103</v>
+      </c>
+      <c r="K73" t="s">
+        <v>199</v>
+      </c>
+      <c r="L73" t="s">
+        <v>103</v>
+      </c>
+      <c r="M73" t="s">
+        <v>173</v>
+      </c>
+      <c r="N73" t="s">
+        <v>103</v>
+      </c>
+      <c r="O73">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C74" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" t="s">
+        <v>167</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>173</v>
+      </c>
+      <c r="H74" t="s">
+        <v>174</v>
+      </c>
+      <c r="I74" t="s">
+        <v>103</v>
+      </c>
+      <c r="J74" t="s">
+        <v>198</v>
+      </c>
+      <c r="K74" t="s">
+        <v>200</v>
+      </c>
+      <c r="L74" t="s">
+        <v>200</v>
+      </c>
+      <c r="M74" t="s">
+        <v>174</v>
+      </c>
+      <c r="N74" t="s">
+        <v>256</v>
+      </c>
+      <c r="O74">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" t="s">
+        <v>97</v>
+      </c>
+      <c r="C75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" t="s">
+        <v>103</v>
+      </c>
+      <c r="F75" t="s">
+        <v>103</v>
+      </c>
+      <c r="G75" t="s">
+        <v>103</v>
+      </c>
+      <c r="H75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I75" t="s">
+        <v>103</v>
+      </c>
+      <c r="J75" t="s">
+        <v>103</v>
+      </c>
+      <c r="K75" t="s">
+        <v>201</v>
+      </c>
+      <c r="L75" t="s">
+        <v>201</v>
+      </c>
+      <c r="M75" t="s">
+        <v>174</v>
+      </c>
+      <c r="N75" t="s">
+        <v>257</v>
+      </c>
+      <c r="O75">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" t="s">
+        <v>103</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>173</v>
+      </c>
+      <c r="H76" t="s">
+        <v>173</v>
+      </c>
+      <c r="I76" t="s">
+        <v>103</v>
+      </c>
+      <c r="J76" t="s">
+        <v>190</v>
+      </c>
+      <c r="K76" t="s">
+        <v>201</v>
+      </c>
+      <c r="L76" t="s">
+        <v>200</v>
+      </c>
+      <c r="M76" t="s">
+        <v>174</v>
+      </c>
+      <c r="N76" t="s">
+        <v>258</v>
+      </c>
+      <c r="O76">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>173</v>
+      </c>
+      <c r="H77" t="s">
+        <v>174</v>
+      </c>
+      <c r="I77" t="s">
+        <v>189</v>
+      </c>
+      <c r="J77" t="s">
+        <v>190</v>
+      </c>
+      <c r="K77" t="s">
+        <v>200</v>
+      </c>
+      <c r="L77" t="s">
+        <v>200</v>
+      </c>
+      <c r="M77" t="s">
+        <v>174</v>
+      </c>
+      <c r="N77" t="s">
+        <v>259</v>
+      </c>
+      <c r="O77">
         <v>19</v>
       </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>12</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>170</v>
+      </c>
+      <c r="E78" t="s">
+        <v>103</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>173</v>
+      </c>
+      <c r="H78" t="s">
+        <v>174</v>
+      </c>
+      <c r="I78" t="s">
+        <v>103</v>
+      </c>
+      <c r="J78" t="s">
+        <v>190</v>
+      </c>
+      <c r="K78" t="s">
+        <v>200</v>
+      </c>
+      <c r="L78" t="s">
+        <v>200</v>
+      </c>
+      <c r="M78" t="s">
+        <v>174</v>
+      </c>
+      <c r="N78" t="s">
+        <v>260</v>
+      </c>
+      <c r="O78">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s">
+        <v>92</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
+      </c>
+      <c r="D79" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>173</v>
+      </c>
+      <c r="H79" t="s">
+        <v>173</v>
+      </c>
+      <c r="I79" t="s">
+        <v>103</v>
+      </c>
+      <c r="J79" t="s">
+        <v>190</v>
+      </c>
+      <c r="K79" t="s">
+        <v>202</v>
+      </c>
+      <c r="L79" t="s">
+        <v>200</v>
+      </c>
+      <c r="M79" t="s">
+        <v>174</v>
+      </c>
+      <c r="N79" t="s">
+        <v>261</v>
+      </c>
+      <c r="O79">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" t="s">
+        <v>103</v>
+      </c>
+      <c r="D80" t="s">
+        <v>172</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80" t="s">
+        <v>173</v>
+      </c>
+      <c r="H80" t="s">
+        <v>174</v>
+      </c>
+      <c r="I80" t="s">
+        <v>103</v>
+      </c>
+      <c r="J80" t="s">
+        <v>103</v>
+      </c>
+      <c r="K80" t="s">
+        <v>201</v>
+      </c>
+      <c r="L80" t="s">
+        <v>200</v>
+      </c>
+      <c r="M80" t="s">
+        <v>174</v>
+      </c>
+      <c r="N80" t="s">
+        <v>262</v>
+      </c>
+      <c r="O80">
         <v>22</v>
       </c>
-      <c r="O2">
-        <v>70</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O80" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>